--- a/assets/archivos/TRANSPARENCIA/ART 63 COMUNES 2022/4TO_TRIMESTRE/FRACCIONES XXXI-XL/FRACC XXXVII/LTAIPT_A63F37B.xlsx
+++ b/assets/archivos/TRANSPARENCIA/ART 63 COMUNES 2022/4TO_TRIMESTRE/FRACCIONES XXXI-XL/FRACC XXXVII/LTAIPT_A63F37B.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="52" uniqueCount="44">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="60" uniqueCount="49">
   <si>
     <t>49000</t>
   </si>
@@ -70,6 +70,12 @@
     <t>436786</t>
   </si>
   <si>
+    <t>571940</t>
+  </si>
+  <si>
+    <t>571941</t>
+  </si>
+  <si>
     <t>436787</t>
   </si>
   <si>
@@ -106,6 +112,12 @@
     <t>Número total de participantes</t>
   </si>
   <si>
+    <t>ESTE CRITERIO APLICA A PARTIR DEL 01/04/2023 -&gt; Total de participantes mujeres</t>
+  </si>
+  <si>
+    <t>ESTE CRITERIO APLICA A PARTIR DEL 01/04/2023 -&gt; Total de participantes hombres</t>
+  </si>
+  <si>
     <t>Respuesta del sujeto obligado a los resultados, descripción sintética de lo que se tomó en cuenta</t>
   </si>
   <si>
@@ -121,31 +133,34 @@
     <t>Nota</t>
   </si>
   <si>
-    <t>3AEF78A82FFEE00050BD143E08F15075</t>
-  </si>
-  <si>
-    <t>2022</t>
-  </si>
-  <si>
-    <t>01/10/2022</t>
-  </si>
-  <si>
-    <t>30/12/2022</t>
+    <t>2023</t>
   </si>
   <si>
     <t>Ver nota</t>
   </si>
   <si>
-    <t>Ver note</t>
+    <t>CB4E50FD1998CF5A5FDD40355E6E8C5D</t>
+  </si>
+  <si>
+    <t>01/01/2023</t>
+  </si>
+  <si>
+    <t>31/03/2023</t>
   </si>
   <si>
     <t/>
   </si>
   <si>
-    <t>03/01/2023</t>
-  </si>
-  <si>
-    <t>Del periodo 01/10/2022 al 30/12/2022 en esta Subdirección de Actividades Paraescolares se encuentra impedida para reportar los mecanismos de participación ciudadana consagradas en el artículo XXXVII, toda vez que dentro del objeto del organismo público desconcentrado, Colegio de Bachilleres del estado de Tlaxcala no se encuentra dentro de su objeto desarrollar este tipo de actividades.</t>
+    <t>Este dato no se requiere para este periodo, de conformidad con las últimas modificaciones a los Lineamientos Técnicos Generales, aprobadas por el Pleno del Consejo Nacional del Sistema Nacional de Transparencia.</t>
+  </si>
+  <si>
+    <t>Ver  nota</t>
+  </si>
+  <si>
+    <t>18/04/2023</t>
+  </si>
+  <si>
+    <t>Del periodo 01/01/2023 al 31/02/2023 en esta Subdirección de Actividades Paraescolares se encuentra impedida para reportar los mecanismos de participación ciudadana consagradas en el artículo XXXVII, toda vez que dentro del objeto del organismo público desconcentrado, Colegio de Bachilleres del estado de Tlaxcala no se encuentra dentro de su objeto desarrollar este tipo de actividades.</t>
   </si>
 </sst>
 </file>
@@ -538,29 +553,30 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:L8"/>
+  <dimension ref="A1:N8"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="36" hidden="1" customWidth="1"/>
+    <col min="1" max="1" width="35.85546875" hidden="1" customWidth="1"/>
     <col min="2" max="2" width="8" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="36.42578125" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="38.5703125" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="49.28515625" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="10.140625" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="26" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="82.42578125" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="73.140625" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="17.5703125" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="20.140625" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="255" bestFit="1" customWidth="1"/>
+    <col min="8" max="9" width="181.85546875" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="82.42578125" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="73.140625" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="17.5703125" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="20.140625" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="255" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="2" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A2" s="3" t="s">
         <v>1</v>
       </c>
@@ -577,7 +593,7 @@
       <c r="H2" s="4"/>
       <c r="I2" s="4"/>
     </row>
-    <row r="3" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A3" s="5" t="s">
         <v>4</v>
       </c>
@@ -592,7 +608,7 @@
       <c r="H3" s="4"/>
       <c r="I3" s="4"/>
     </row>
-    <row r="4" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="B4" t="s">
         <v>6</v>
       </c>
@@ -612,22 +628,28 @@
         <v>9</v>
       </c>
       <c r="H4" t="s">
+        <v>9</v>
+      </c>
+      <c r="I4" t="s">
+        <v>9</v>
+      </c>
+      <c r="J4" t="s">
         <v>8</v>
       </c>
-      <c r="I4" t="s">
+      <c r="K4" t="s">
         <v>8</v>
       </c>
-      <c r="J4" t="s">
+      <c r="L4" t="s">
         <v>7</v>
       </c>
-      <c r="K4" t="s">
+      <c r="M4" t="s">
         <v>10</v>
       </c>
-      <c r="L4" t="s">
+      <c r="N4" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="5" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="B5" t="s">
         <v>12</v>
       </c>
@@ -661,10 +683,16 @@
       <c r="L5" t="s">
         <v>22</v>
       </c>
+      <c r="M5" t="s">
+        <v>23</v>
+      </c>
+      <c r="N5" t="s">
+        <v>24</v>
+      </c>
     </row>
-    <row r="6" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A6" s="3" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="B6" s="4"/>
       <c r="C6" s="4"/>
@@ -677,83 +705,97 @@
       <c r="J6" s="4"/>
       <c r="K6" s="4"/>
       <c r="L6" s="4"/>
+      <c r="M6" s="4"/>
+      <c r="N6" s="4"/>
     </row>
-    <row r="7" spans="1:12" ht="26.25" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:14" ht="26.25" x14ac:dyDescent="0.25">
       <c r="B7" s="1" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="F7" s="1" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="G7" s="1" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="H7" s="1" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="I7" s="1" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="J7" s="1" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="K7" s="1" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="L7" s="1" t="s">
-        <v>34</v>
+        <v>36</v>
+      </c>
+      <c r="M7" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="N7" s="1" t="s">
+        <v>38</v>
       </c>
     </row>
-    <row r="8" spans="1:12" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:14" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="2" t="s">
-        <v>35</v>
+        <v>41</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>37</v>
+        <v>42</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="F8" s="2" t="s">
         <v>40</v>
       </c>
       <c r="G8" s="2" t="s">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="H8" s="2" t="s">
-        <v>39</v>
+        <v>45</v>
       </c>
       <c r="I8" s="2" t="s">
-        <v>39</v>
+        <v>45</v>
       </c>
       <c r="J8" s="2" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="K8" s="2" t="s">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="L8" s="2" t="s">
-        <v>43</v>
+        <v>47</v>
+      </c>
+      <c r="M8" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="N8" s="2" t="s">
+        <v>48</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="7">
-    <mergeCell ref="A6:L6"/>
+    <mergeCell ref="A6:N6"/>
     <mergeCell ref="A2:C2"/>
     <mergeCell ref="D2:F2"/>
     <mergeCell ref="G2:I2"/>
